--- a/automotive_forms/001_vehicle_inspection_knowledge_quiz--automotive_forms.xlsx
+++ b/automotive_forms/001_vehicle_inspection_knowledge_quiz--automotive_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,20 +515,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_2</t>
+          <t>engine_type</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>engine</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Engine Type</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>What is the engine type of a typical vehicle?</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -538,23 +542,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_3</t>
+          <t>brake_fluid_level_check</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>brake_system</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Brake Fluid Level Check</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>How often should you check the brake fluid level?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_4</t>
+          <t>suspension_function</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>vehicle_system</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Suspension System Function</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>What is the primary function of the suspension system?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_5</t>
+          <t>coolant_temp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>transmission</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Coolant Temperature Check</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>At what temperature should you check the coolant level?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -607,43 +623,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_6</t>
+          <t>steering_purpose</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>exhaust_system</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Steering System Purpose</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>What is the purpose of the steering system?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_7</t>
+          <t>tire_inspection_frequency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>suspension</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Tire Inspection Frequency</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>How often should you inspect the tires?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -653,412 +677,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_8</t>
+          <t>final_submission</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>steering_system</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Final Submission</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Record your final results.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_9</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>brakes</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_10</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>steering</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_11</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>suspension</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_12</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>engine</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_13</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>transmission</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_14</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>brakes</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_15</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>steering</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_16</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>suspension</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>vehicle_system</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_18</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>engine</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_19</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>steering_system</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_20</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>transmission</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_21</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>vehicle_system</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_22</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>engine</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_23</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>steering_system</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_24</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>transmission</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>vehicle_inspection_knowledge_quiz_25</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>final_submission</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1075,12 +712,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1103,170 +740,408 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_4_choices</t>
+          <t>engine_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>v8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>V8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_4_choices</t>
+          <t>engine_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>v6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>V6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_7_choices</t>
+          <t>engine_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>v4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>V4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_7_choices</t>
+          <t>engine_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>inline_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Inline 4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_11_choices</t>
+          <t>brake_fluid_level_check_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_11_choices</t>
+          <t>brake_fluid_level_check_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_16_choices</t>
+          <t>brake_fluid_level_check_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_16_choices</t>
+          <t>brake_fluid_level_check_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>every_6_months</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Every 6 months</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_23_choices</t>
+          <t>suspension_function_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>supports_vehicle_stability</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Supports vehicle stability</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vehicle_inspection_knowledge_quiz_23_choices</t>
+          <t>suspension_function_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>improves_steering_response</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Improves steering response</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>suspension_function_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>reduces_vibration</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Reduces vibration</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>suspension_function_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>increases_vehicle_height</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Increases vehicle height</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>coolant_temp_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>hot</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>coolant_temp_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>cold</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>coolant_temp_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>room_temperature</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Room Temperature</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>coolant_temp_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>steering_purpose_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>to_turn_the_vehicle</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>To turn the vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>steering_purpose_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>to_steer_the_vehicle</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>To steer the vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>steering_purpose_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>to_improve_vehicle_stability</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>To improve vehicle stability</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>steering_purpose_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>to_reduce_fuel_consumption</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>To reduce fuel consumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>tire_inspection_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>tire_inspection_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>tire_inspection_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>tire_inspection_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>every_6_months</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Every 6 months</t>
         </is>
       </c>
     </row>
